--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eirar\Polla\Pauta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F8762F-DD22-4C54-91F2-C284511D616A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEBC965-A7F6-41FE-8DB6-D836B4710375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="23">
   <si>
     <t>Partido 1</t>
   </si>
@@ -96,6 +96,15 @@
   </si>
   <si>
     <t>Partido 16</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>Pasa Brasil</t>
   </si>
 </sst>
 </file>
@@ -582,18 +591,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1176-9B5F-4509-AEB9-C4D2AF7AA58E}">
   <dimension ref="B1:I64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.53125" customWidth="1"/>
-    <col min="2" max="2" width="14.46484375" customWidth="1"/>
-    <col min="3" max="3" width="3.53125" customWidth="1"/>
-    <col min="4" max="4" width="14.796875" customWidth="1"/>
-    <col min="8" max="8" width="13.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="3.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.08984375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
@@ -601,36 +610,44 @@
       <c r="D2" s="8"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Brasil</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="1"/>
+    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="H3" s="5" t="str">
         <f>"Pasa "&amp; D3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Alemania</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="9"/>
+    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="9" t="s">
+        <v>22</v>
+      </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="6" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
@@ -644,7 +661,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="1"/>
       <c r="C7" s="4" t="s">
         <v>1</v>
@@ -658,7 +675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="9"/>
       <c r="C8" s="10"/>
       <c r="D8" s="3"/>
@@ -666,8 +683,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="10" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
@@ -681,7 +698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
         <v>1</v>
@@ -695,7 +712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
       <c r="D12" s="3"/>
@@ -703,8 +720,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="14" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
@@ -718,7 +735,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="1"/>
       <c r="C15" s="4" t="s">
         <v>1</v>
@@ -732,7 +749,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
       <c r="D16" s="3"/>
@@ -740,8 +757,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="18" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="6" t="s">
         <v>5</v>
       </c>
@@ -755,7 +772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="1"/>
       <c r="C19" s="4" t="s">
         <v>1</v>
@@ -769,7 +786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="9"/>
       <c r="C20" s="10"/>
       <c r="D20" s="3"/>
@@ -777,8 +794,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="22" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
@@ -792,7 +809,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
       <c r="C23" s="4" t="s">
         <v>1</v>
@@ -806,7 +823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="9"/>
       <c r="C24" s="10"/>
       <c r="D24" s="3"/>
@@ -814,8 +831,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="26" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
@@ -829,7 +846,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="1"/>
       <c r="C27" s="4" t="s">
         <v>1</v>
@@ -843,7 +860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" s="9"/>
       <c r="C28" s="10"/>
       <c r="D28" s="3"/>
@@ -851,8 +868,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="30" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
@@ -866,7 +883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
         <v>1</v>
@@ -880,7 +897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="9"/>
       <c r="C32" s="10"/>
       <c r="D32" s="3"/>
@@ -888,8 +905,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="34" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="34" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="6" t="s">
         <v>12</v>
       </c>
@@ -903,7 +920,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="1"/>
       <c r="C35" s="4" t="s">
         <v>1</v>
@@ -917,7 +934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="9"/>
       <c r="C36" s="10"/>
       <c r="D36" s="3"/>
@@ -925,8 +942,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="6" t="s">
         <v>13</v>
       </c>
@@ -940,7 +957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="1"/>
       <c r="C39" s="4" t="s">
         <v>1</v>
@@ -954,7 +971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="9"/>
       <c r="C40" s="10"/>
       <c r="D40" s="3"/>
@@ -962,8 +979,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="42" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="42" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="6" t="s">
         <v>14</v>
       </c>
@@ -977,7 +994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="43" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="1"/>
       <c r="C43" s="4" t="s">
         <v>1</v>
@@ -991,7 +1008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="9"/>
       <c r="C44" s="10"/>
       <c r="D44" s="3"/>
@@ -999,8 +1016,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="46" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="6" t="s">
         <v>15</v>
       </c>
@@ -1014,7 +1031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="1"/>
       <c r="C47" s="4" t="s">
         <v>1</v>
@@ -1028,7 +1045,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="9"/>
       <c r="C48" s="10"/>
       <c r="D48" s="3"/>
@@ -1036,8 +1053,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="50" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="49" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="50" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="6" t="s">
         <v>16</v>
       </c>
@@ -1051,7 +1068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="51" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="1"/>
       <c r="C51" s="4" t="s">
         <v>1</v>
@@ -1065,7 +1082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="9"/>
       <c r="C52" s="10"/>
       <c r="D52" s="3"/>
@@ -1073,8 +1090,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="54" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="53" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="54" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="6" t="s">
         <v>17</v>
       </c>
@@ -1088,7 +1105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="1"/>
       <c r="C55" s="4" t="s">
         <v>1</v>
@@ -1102,7 +1119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="56" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="9"/>
       <c r="C56" s="10"/>
       <c r="D56" s="3"/>
@@ -1110,8 +1127,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="58" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="57" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="58" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="6" t="s">
         <v>18</v>
       </c>
@@ -1125,7 +1142,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="1"/>
       <c r="C59" s="4" t="s">
         <v>1</v>
@@ -1139,7 +1156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="60" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="9"/>
       <c r="C60" s="10"/>
       <c r="D60" s="3"/>
@@ -1147,8 +1164,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="62" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="62" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="6" t="s">
         <v>19</v>
       </c>
@@ -1162,7 +1179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="1"/>
       <c r="C63" s="4" t="s">
         <v>1</v>
@@ -1176,7 +1193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="64" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="9"/>
       <c r="C64" s="10"/>
       <c r="D64" s="3"/>
@@ -1186,31 +1203,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:D50"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="B52:C52"/>
@@ -1218,6 +1210,31 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEBC965-A7F6-41FE-8DB6-D836B4710375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D93875-9A18-422B-8698-695AC8E903C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="20">
   <si>
     <t>Partido 1</t>
   </si>
@@ -96,15 +96,6 @@
   </si>
   <si>
     <t>Partido 16</t>
-  </si>
-  <si>
-    <t>Brasil</t>
-  </si>
-  <si>
-    <t>Alemania</t>
-  </si>
-  <si>
-    <t>Pasa Brasil</t>
   </si>
 </sst>
 </file>
@@ -610,38 +601,30 @@
       <c r="D2" s="8"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
-        <v>Pasa Brasil</v>
+        <v xml:space="preserve">Pasa </v>
       </c>
       <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="H3" s="5" t="str">
         <f>"Pasa "&amp; D3</f>
-        <v>Pasa Alemania</v>
+        <v xml:space="preserve">Pasa </v>
       </c>
       <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9" t="s">
-        <v>22</v>
-      </c>
+      <c r="B4" s="9"/>
       <c r="C4" s="10"/>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="I4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1203,6 +1186,31 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:D50"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="B52:C52"/>
@@ -1210,31 +1218,6 @@
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub Clones\polla-mundial\Pauta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D93875-9A18-422B-8698-695AC8E903C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70C9330-987D-4EB9-891E-DF17C793C48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,41 +33,71 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t>Partido 1</t>
   </si>
   <si>
+    <t>En los 90</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
     <t>vs</t>
   </si>
   <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>En tiempo extra</t>
+  </si>
+  <si>
+    <t>En penales</t>
+  </si>
+  <si>
     <t>Partido 2</t>
   </si>
   <si>
+    <t>Brasil</t>
+  </si>
+  <si>
     <t>Partido 3</t>
   </si>
   <si>
+    <t>Alemania</t>
+  </si>
+  <si>
     <t>Partido 4</t>
   </si>
   <si>
+    <t>Holanda</t>
+  </si>
+  <si>
+    <t>Marruecos</t>
+  </si>
+  <si>
     <t>Partido 5</t>
   </si>
   <si>
-    <t>En los 90</t>
-  </si>
-  <si>
-    <t>En tiempo extra</t>
-  </si>
-  <si>
-    <t>En penales</t>
+    <t>Costa de Marfil</t>
+  </si>
+  <si>
+    <t>Noruega</t>
   </si>
   <si>
     <t>Partido 6</t>
   </si>
   <si>
+    <t>Francia</t>
+  </si>
+  <si>
     <t>Partido 7</t>
   </si>
   <si>
+    <t>México</t>
+  </si>
+  <si>
     <t>Partido 8</t>
   </si>
   <si>
@@ -80,22 +107,91 @@
     <t>Partido 10</t>
   </si>
   <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>Bosnia y Herzegovina</t>
+  </si>
+  <si>
     <t>Partido 11</t>
   </si>
   <si>
+    <t>España</t>
+  </si>
+  <si>
     <t>Partido 12</t>
   </si>
   <si>
     <t>Partido 13</t>
   </si>
   <si>
+    <t xml:space="preserve">Suiza </t>
+  </si>
+  <si>
     <t>Partido 14</t>
   </si>
   <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>Partido 15</t>
   </si>
   <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Cabo Verde</t>
+  </si>
+  <si>
     <t>Partido 16</t>
+  </si>
+  <si>
+    <t>Japón</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Inglaterra</t>
+  </si>
+  <si>
+    <t>RD Congo</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Croacia</t>
+  </si>
+  <si>
+    <t>Argelia</t>
+  </si>
+  <si>
+    <t>Egipto</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Pasa Canadá</t>
   </si>
 </sst>
 </file>
@@ -219,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -232,21 +328,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1176-9B5F-4509-AEB9-C4D2AF7AA58E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:I64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -592,638 +681,706 @@
     <col min="9" max="9" width="13.08984375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
+    <row r="1" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="7"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Sudáfrica</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="H3" s="5" t="str">
         <f>"Pasa "&amp; D3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Canadá</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="3"/>
-      <c r="I4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="7"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Brasil</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="H7" s="5" t="str">
         <f>"Pasa "&amp; D7</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Japón</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="3"/>
       <c r="I8" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="7"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Alemania</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="H11" s="5" t="str">
         <f>"Pasa "&amp; D11</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Paraguay</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="3"/>
       <c r="I12" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="7"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Holanda</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="C15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H15" s="5" t="str">
         <f>"Pasa "&amp; D15</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Marruecos</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="3"/>
       <c r="I16" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="7"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Costa de Marfil</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C19" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="H19" s="5" t="str">
         <f>"Pasa "&amp; D19</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Noruega</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="3"/>
       <c r="I20" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="7"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Francia</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C23" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="H23" s="5" t="str">
         <f>"Pasa "&amp; D23</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Suecia</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="3"/>
       <c r="I24" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="7"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa México</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="C27" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H27" s="5" t="str">
         <f>"Pasa "&amp; D27</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Ecuador</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="3"/>
       <c r="I28" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="7"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Inglaterra</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="C31" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="H31" s="5" t="str">
         <f>"Pasa "&amp; D31</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa RD Congo</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="34" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="34" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="7"/>
       <c r="H34" s="5" t="str">
         <f>"Pasa "&amp;B35</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Bélgica</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="C35" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="H35" s="5" t="str">
         <f>"Pasa "&amp; D35</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Senegal</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="9"/>
-      <c r="C36" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="3"/>
       <c r="I36" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="38" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="7"/>
       <c r="H38" s="5" t="str">
         <f>"Pasa "&amp;B39</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Estados Unidos</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="C39" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H39" s="5" t="str">
         <f>"Pasa "&amp; D39</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Bosnia y Herzegovina</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="9"/>
-      <c r="C40" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="6"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="3"/>
       <c r="I40" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="42" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="42" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="7"/>
       <c r="H42" s="5" t="str">
         <f>"Pasa "&amp;B43</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa España</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C43" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="H43" s="5" t="str">
         <f>"Pasa "&amp; D43</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Austria</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="9"/>
-      <c r="C44" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="6"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="3"/>
       <c r="I44" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="46" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="7"/>
       <c r="H46" s="5" t="str">
         <f>"Pasa "&amp;B47</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Portugal</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="C47" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="H47" s="5" t="str">
         <f>"Pasa "&amp; D47</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Croacia</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
       <c r="D48" s="3"/>
       <c r="I48" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="50" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="50" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="7"/>
       <c r="H50" s="5" t="str">
         <f>"Pasa "&amp;B51</f>
-        <v xml:space="preserve">Pasa </v>
+        <v xml:space="preserve">Pasa Suiza </v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="C51" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="H51" s="5" t="str">
         <f>"Pasa "&amp; D51</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Argelia</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="9"/>
-      <c r="C52" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="6"/>
+      <c r="C52" s="7"/>
       <c r="D52" s="3"/>
       <c r="I52" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="54" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="54" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="9"/>
+      <c r="D54" s="7"/>
       <c r="H54" s="5" t="str">
         <f>"Pasa "&amp;B55</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Australia</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="C55" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="H55" s="5" t="str">
         <f>"Pasa "&amp; D55</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Egipto</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="9"/>
-      <c r="C56" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="6"/>
+      <c r="C56" s="7"/>
       <c r="D56" s="3"/>
       <c r="I56" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="58" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="58" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B58" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="7"/>
       <c r="H58" s="5" t="str">
         <f>"Pasa "&amp;B59</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Argentina</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B59" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B59" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="C59" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="H59" s="5" t="str">
         <f>"Pasa "&amp; D59</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Cabo Verde</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="9"/>
-      <c r="C60" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B60" s="6"/>
+      <c r="C60" s="7"/>
       <c r="D60" s="3"/>
       <c r="I60" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="62" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="62" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B62" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62" s="9"/>
+      <c r="D62" s="7"/>
       <c r="H62" s="5" t="str">
         <f>"Pasa "&amp;B63</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Colombia</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B63" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B63" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="C63" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="H63" s="5" t="str">
         <f>"Pasa "&amp; D63</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Ghana</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B64" s="6"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="3"/>
       <c r="I64" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>H2:H3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4 D8 D12 D16 D20 D24 D28 D32 D36 D40 D44 D48 D52 D56 D60 D64" xr:uid="{6B5BD9C5-77E0-451B-B309-FF5A210DF639}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4 D8 D12 D16 D20 D24 D28 D32 D36 D40 D44 D48 D52 D56 D60 D64" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$I$2:$I$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70C9330-987D-4EB9-891E-DF17C793C48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480508D6-B565-430D-BA80-72B839BE16EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
   <si>
     <t>Partido 1</t>
   </si>
@@ -189,9 +189,6 @@
   </si>
   <si>
     <t>Ghana</t>
-  </si>
-  <si>
-    <t>Pasa Canadá</t>
   </si>
 </sst>
 </file>
@@ -715,13 +712,9 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
-        <v>52</v>
-      </c>
+      <c r="B4" s="6"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
@@ -1343,6 +1336,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1359,22 +1368,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480508D6-B565-430D-BA80-72B839BE16EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970932DF-2F8A-4DED-950F-98F794A51F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t>Partido 1</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>Ghana</t>
+  </si>
+  <si>
+    <t>Pasa Canadá</t>
   </si>
 </sst>
 </file>
@@ -712,9 +715,13 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
@@ -1336,22 +1343,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1368,6 +1359,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970932DF-2F8A-4DED-950F-98F794A51F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C0E0B3-F664-4E9A-AD08-D01C57C959F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
   <si>
     <t>Partido 1</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Pasa Canadá</t>
+  </si>
+  <si>
+    <t>Pasa Brasil</t>
   </si>
 </sst>
 </file>
@@ -760,9 +763,13 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1343,6 +1350,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1359,22 +1382,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C0E0B3-F664-4E9A-AD08-D01C57C959F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793B728B-363D-49F8-B549-2CF42D85451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="55">
   <si>
     <t>Partido 1</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>Pasa Brasil</t>
+  </si>
+  <si>
+    <t>Pasa Paraguay</t>
   </si>
 </sst>
 </file>
@@ -808,9 +811,13 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="6"/>
+      <c r="B12" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I12" s="5" t="s">
         <v>6</v>
       </c>
@@ -1350,22 +1357,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1382,6 +1373,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793B728B-363D-49F8-B549-2CF42D85451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BB6FF5-47AA-489B-8EB1-4ABF9C531352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
   <si>
     <t>Partido 1</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Pasa Paraguay</t>
+  </si>
+  <si>
+    <t>Pasa Holanda</t>
   </si>
 </sst>
 </file>
@@ -856,9 +859,13 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="6"/>
+      <c r="B16" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I16" s="5" t="s">
         <v>6</v>
       </c>
@@ -1357,6 +1364,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1373,22 +1396,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BB6FF5-47AA-489B-8EB1-4ABF9C531352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7305CD-34FE-44C9-B16B-0D674B93612E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -864,7 +864,7 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>6</v>

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7305CD-34FE-44C9-B16B-0D674B93612E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875DB32A-B8AF-42A3-BB13-A91046446D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -200,7 +200,7 @@
     <t>Pasa Paraguay</t>
   </si>
   <si>
-    <t>Pasa Holanda</t>
+    <t>Pasa Marruecos</t>
   </si>
 </sst>
 </file>

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875DB32A-B8AF-42A3-BB13-A91046446D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93F1D4C-572E-4806-8E4B-7E703EAAF111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
   <si>
     <t>Partido 1</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>Pasa Marruecos</t>
+  </si>
+  <si>
+    <t>Pasa Noruega</t>
   </si>
 </sst>
 </file>
@@ -904,9 +907,13 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I20" s="5" t="s">
         <v>6</v>
       </c>
@@ -1364,22 +1371,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1396,6 +1387,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93F1D4C-572E-4806-8E4B-7E703EAAF111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDBA528-CC04-42F4-B3B6-D2A8B680FA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
   <si>
     <t>Partido 1</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>Pasa Noruega</t>
+  </si>
+  <si>
+    <t>Pasa Francia</t>
   </si>
 </sst>
 </file>
@@ -952,9 +955,13 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="6"/>
+      <c r="B24" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I24" s="5" t="s">
         <v>6</v>
       </c>
@@ -1371,6 +1378,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1387,22 +1410,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDBA528-CC04-42F4-B3B6-D2A8B680FA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE2EA1D-D993-4117-B684-94EEFAC66E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Partido 1</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>Pasa Francia</t>
+  </si>
+  <si>
+    <t>Pasa México</t>
   </si>
 </sst>
 </file>
@@ -1000,9 +1003,13 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="6"/>
+      <c r="B28" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="C28" s="7"/>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I28" s="5" t="s">
         <v>6</v>
       </c>
@@ -1378,22 +1385,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1410,6 +1401,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE2EA1D-D993-4117-B684-94EEFAC66E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B8EE59-9D6B-40BC-83D6-2F4B07572175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
   <si>
     <t>Partido 1</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>Pasa México</t>
+  </si>
+  <si>
+    <t>Pasa Inglaterra</t>
   </si>
 </sst>
 </file>
@@ -1048,9 +1051,13 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="6"/>
+      <c r="B32" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="C32" s="7"/>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I32" s="5" t="s">
         <v>6</v>
       </c>
@@ -1385,6 +1392,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1401,22 +1424,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B8EE59-9D6B-40BC-83D6-2F4B07572175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D43F25-9103-4D50-8438-8579F9FB05F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
   <si>
     <t>Partido 1</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>Pasa Inglaterra</t>
+  </si>
+  <si>
+    <t>Pasa Senegal</t>
   </si>
 </sst>
 </file>
@@ -1096,9 +1099,13 @@
       </c>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="6"/>
+      <c r="B36" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I36" s="5" t="s">
         <v>6</v>
       </c>
@@ -1392,22 +1399,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1424,6 +1415,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D43F25-9103-4D50-8438-8579F9FB05F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D542208-6952-45BA-AC0B-8CDDDA82AA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="68">
   <si>
     <t>Partido 1</t>
   </si>
@@ -216,6 +216,27 @@
   </si>
   <si>
     <t>Pasa Senegal</t>
+  </si>
+  <si>
+    <t>Pasa Estados Unidos</t>
+  </si>
+  <si>
+    <t>Pasa España</t>
+  </si>
+  <si>
+    <t>Pasa Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasa Suiza </t>
+  </si>
+  <si>
+    <t>Pasa Egipto</t>
+  </si>
+  <si>
+    <t>Pasa Argentina</t>
+  </si>
+  <si>
+    <t>Pasa Colombia</t>
   </si>
 </sst>
 </file>
@@ -1144,9 +1165,13 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="6"/>
+      <c r="B40" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I40" s="5" t="s">
         <v>6</v>
       </c>
@@ -1185,9 +1210,13 @@
       </c>
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="6"/>
+      <c r="B44" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="C44" s="7"/>
-      <c r="D44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I44" s="5" t="s">
         <v>6</v>
       </c>
@@ -1226,9 +1255,13 @@
       </c>
     </row>
     <row r="48" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="6"/>
+      <c r="B48" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I48" s="5" t="s">
         <v>6</v>
       </c>
@@ -1267,9 +1300,13 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="6"/>
+      <c r="B52" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="C52" s="7"/>
-      <c r="D52" s="3"/>
+      <c r="D52" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I52" s="5" t="s">
         <v>6</v>
       </c>
@@ -1308,9 +1345,13 @@
       </c>
     </row>
     <row r="56" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="6"/>
+      <c r="B56" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="C56" s="7"/>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I56" s="5" t="s">
         <v>6</v>
       </c>
@@ -1349,9 +1390,13 @@
       </c>
     </row>
     <row r="60" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="6"/>
+      <c r="B60" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="C60" s="7"/>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I60" s="5" t="s">
         <v>6</v>
       </c>
@@ -1390,15 +1435,35 @@
       </c>
     </row>
     <row r="64" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="6"/>
+      <c r="B64" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="C64" s="7"/>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1415,22 +1480,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D542208-6952-45BA-AC0B-8CDDDA82AA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D1508C-F82A-4A20-AD26-188ACF5F7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
   <si>
     <t>Partido 1</t>
   </si>
@@ -216,27 +216,6 @@
   </si>
   <si>
     <t>Pasa Senegal</t>
-  </si>
-  <si>
-    <t>Pasa Estados Unidos</t>
-  </si>
-  <si>
-    <t>Pasa España</t>
-  </si>
-  <si>
-    <t>Pasa Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasa Suiza </t>
-  </si>
-  <si>
-    <t>Pasa Egipto</t>
-  </si>
-  <si>
-    <t>Pasa Argentina</t>
-  </si>
-  <si>
-    <t>Pasa Colombia</t>
   </si>
 </sst>
 </file>
@@ -1165,13 +1144,9 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="6" t="s">
-        <v>61</v>
-      </c>
+      <c r="B40" s="6"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D40" s="3"/>
       <c r="I40" s="5" t="s">
         <v>6</v>
       </c>
@@ -1210,13 +1185,9 @@
       </c>
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="B44" s="6"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D44" s="3"/>
       <c r="I44" s="5" t="s">
         <v>6</v>
       </c>
@@ -1255,13 +1226,9 @@
       </c>
     </row>
     <row r="48" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="6" t="s">
-        <v>63</v>
-      </c>
+      <c r="B48" s="6"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D48" s="3"/>
       <c r="I48" s="5" t="s">
         <v>6</v>
       </c>
@@ -1300,13 +1267,9 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="B52" s="6"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="D52" s="3"/>
       <c r="I52" s="5" t="s">
         <v>6</v>
       </c>
@@ -1345,13 +1308,9 @@
       </c>
     </row>
     <row r="56" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="6" t="s">
-        <v>65</v>
-      </c>
+      <c r="B56" s="6"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D56" s="3"/>
       <c r="I56" s="5" t="s">
         <v>6</v>
       </c>
@@ -1390,13 +1349,9 @@
       </c>
     </row>
     <row r="60" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="B60" s="6"/>
       <c r="C60" s="7"/>
-      <c r="D60" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D60" s="3"/>
       <c r="I60" s="5" t="s">
         <v>6</v>
       </c>
@@ -1435,35 +1390,15 @@
       </c>
     </row>
     <row r="64" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="6" t="s">
-        <v>67</v>
-      </c>
+      <c r="B64" s="6"/>
       <c r="C64" s="7"/>
-      <c r="D64" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D64" s="3"/>
       <c r="I64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1480,6 +1415,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D1508C-F82A-4A20-AD26-188ACF5F7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4C3100-81C0-4FDC-9171-AA0172C14626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -215,7 +215,7 @@
     <t>Pasa Inglaterra</t>
   </si>
   <si>
-    <t>Pasa Senegal</t>
+    <t>Pasa Bélgica</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>6</v>
@@ -1399,6 +1399,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1415,22 +1431,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4C3100-81C0-4FDC-9171-AA0172C14626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D65BD3-863F-4DB5-8311-7A927B0A9B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Partido 1</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>Pasa Bélgica</t>
+  </si>
+  <si>
+    <t>Pasa Estados Unidos</t>
   </si>
 </sst>
 </file>
@@ -1144,9 +1147,13 @@
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="6"/>
+      <c r="B40" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I40" s="5" t="s">
         <v>6</v>
       </c>
@@ -1399,22 +1406,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1431,6 +1422,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D65BD3-863F-4DB5-8311-7A927B0A9B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8363F892-EC64-47D0-92CE-FD76C0EA88C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="63">
   <si>
     <t>Partido 1</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Pasa Estados Unidos</t>
+  </si>
+  <si>
+    <t>Pasa España</t>
   </si>
 </sst>
 </file>
@@ -1192,9 +1195,13 @@
       </c>
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="6"/>
+      <c r="B44" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="C44" s="7"/>
-      <c r="D44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I44" s="5" t="s">
         <v>6</v>
       </c>
@@ -1406,6 +1413,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1422,22 +1445,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8363F892-EC64-47D0-92CE-FD76C0EA88C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EDE195-9599-4BD4-8147-7042F691EF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="65">
   <si>
     <t>Partido 1</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>Pasa España</t>
+  </si>
+  <si>
+    <t>Pasa Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasa Suiza </t>
   </si>
 </sst>
 </file>
@@ -1240,9 +1246,13 @@
       </c>
     </row>
     <row r="48" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="6"/>
+      <c r="B48" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I48" s="5" t="s">
         <v>6</v>
       </c>
@@ -1281,9 +1291,13 @@
       </c>
     </row>
     <row r="52" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="6"/>
+      <c r="B52" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="C52" s="7"/>
-      <c r="D52" s="3"/>
+      <c r="D52" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I52" s="5" t="s">
         <v>6</v>
       </c>
@@ -1413,22 +1427,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1445,6 +1443,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EDE195-9599-4BD4-8147-7042F691EF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91DCA11-5FA8-4EC4-9C18-2F5BBD54B0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
   <si>
     <t>Partido 1</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pasa Suiza </t>
+  </si>
+  <si>
+    <t>Pasa Egipto</t>
   </si>
 </sst>
 </file>
@@ -1336,9 +1339,13 @@
       </c>
     </row>
     <row r="56" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="6"/>
+      <c r="B56" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="C56" s="7"/>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I56" s="5" t="s">
         <v>6</v>
       </c>
@@ -1427,6 +1434,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1443,22 +1466,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91DCA11-5FA8-4EC4-9C18-2F5BBD54B0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B18F1FE-C65E-4716-80E6-3A98E2AB6995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="67">
   <si>
     <t>Partido 1</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>Pasa Egipto</t>
+  </si>
+  <si>
+    <t>Pasa Argentina</t>
   </si>
 </sst>
 </file>
@@ -1384,9 +1387,13 @@
       </c>
     </row>
     <row r="60" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="6"/>
+      <c r="B60" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="C60" s="7"/>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="I60" s="5" t="s">
         <v>6</v>
       </c>
@@ -1434,22 +1441,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1466,6 +1457,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B18F1FE-C65E-4716-80E6-3A98E2AB6995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE29031F-2D94-43C9-8A31-0C9F63F3FD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="68">
   <si>
     <t>Partido 1</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>Pasa Argentina</t>
+  </si>
+  <si>
+    <t>Pasa Colombia</t>
   </si>
 </sst>
 </file>
@@ -1432,15 +1435,35 @@
       </c>
     </row>
     <row r="64" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="6"/>
+      <c r="B64" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="C64" s="7"/>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I64" s="5" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1457,22 +1480,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Pauta/E02Pauta.xlsx
+++ b/Pauta/E02Pauta.xlsx
@@ -1448,22 +1448,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B62:D62"/>
@@ -1480,6 +1464,22 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32 B36 B40 B44 B48 B52 B56 B60 B64" xr:uid="{00000000-0002-0000-0000-000000000000}">
